--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,66 +912,69 @@
   </si>
   <si>
     <t>214
-140</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>R$ 1.311.737,43</t>
-  </si>
-  <si>
-    <t>R$ 8.744,92
-R$ 8.993,50</t>
-  </si>
-  <si>
-    <t>1.0%
-3.9%</t>
+169</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 1.575.495,35</t>
+  </si>
+  <si>
+    <t>R$ 8.752,75
+R$ 8.991,71</t>
+  </si>
+  <si>
+    <t>2.1%
+4.5%</t>
   </si>
   <si>
     <t>93.3</t>
   </si>
   <si>
-    <t>(2.8%)</t>
-  </si>
-  <si>
-    <t>31.1%</t>
-  </si>
-  <si>
-    <t>(5.5%)</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>62.6%</t>
-  </si>
-  <si>
-    <t>13.1%</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>20.1</t>
-  </si>
-  <si>
-    <t>66.6%</t>
-  </si>
-  <si>
-    <t>-R$ 42.219,28</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>(2.3%)</t>
+  </si>
+  <si>
+    <t>14.5%</t>
+  </si>
+  <si>
+    <t>(25.1%)</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>60.7%</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>64.5%</t>
+  </si>
+  <si>
+    <t>-R$ 45.977,61</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1408,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>2.0969135802469134</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>5.9423859999999999</v>
+      </c>
       <c r="AD3" s="8">
         <v>12.90534938271605</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.952044339622641</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>14.924842</v>
+      </c>
       <c r="AD4" s="8">
         <v>20.15754716981132</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>17.680929807692308</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>25.779399000000002</v>
+      </c>
       <c r="AD5" s="8">
         <v>31.159501869158877</v>
       </c>
@@ -2152,7 +2161,7 @@
         <v>19508</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C7" s="4">
         <v>44</v>
@@ -2188,25 +2197,61 @@
       <c t="s" r="N7" s="4">
         <v>52</v>
       </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="6"/>
+      <c r="O7" s="5">
+        <v>10831.91</v>
+      </c>
+      <c r="P7" s="5">
+        <v>10831.91</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0.094874404773336085</v>
+      </c>
+      <c r="R7" s="7">
+        <v>117</v>
+      </c>
+      <c r="S7" s="6">
+        <v>0.073394495412844041</v>
+      </c>
+      <c r="T7" s="6">
+        <v>0.3381100470738771</v>
+      </c>
+      <c r="U7" s="6">
+        <v>0.0080251405338486008</v>
+      </c>
+      <c r="V7" s="6">
+        <v>0.041526286684435157</v>
+      </c>
+      <c r="W7" s="6">
+        <v>0.015055424204964776</v>
+      </c>
+      <c r="X7" s="8">
+        <v>26.302451470588238</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>0.073529411764705885</v>
+      </c>
+      <c r="AA7" s="8">
+        <v>6.968018018018018</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>4.0639705882352946</v>
+      </c>
+      <c r="AC7" s="8">
+        <v>11.443921</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>18.446569117647059</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF7" s="9"/>
-      <c r="AG7" s="5"/>
+      <c r="AG7" s="5">
+        <v>-107.8</v>
+      </c>
       <c r="AH7" s="10">
         <v>5</v>
       </c>
@@ -2301,10 +2346,10 @@
         <v>0.1454545454545455</v>
       </c>
       <c r="T8" s="6">
-        <v>0.29799603743853187</v>
+        <v>0.30928232640030417</v>
       </c>
       <c r="U8" s="6">
-        <v>-0.028663263375171031</v>
+        <v>-0.01737697441339876</v>
       </c>
       <c r="V8" s="6">
         <v>0.021367397641822463</v>
@@ -2327,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>2.7983870967741935</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>9.5594979999999996</v>
+      </c>
       <c r="AD8" s="8">
         <v>16.509319354838709</v>
       </c>
@@ -2456,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>4.8921936708860754</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>9.4128190000000007</v>
+      </c>
       <c r="AD9" s="8">
         <v>15.41666625</v>
       </c>
@@ -2583,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>3.3016256097560972</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.1837540000000004</v>
+      </c>
       <c r="AD10" s="8">
         <v>14.979116867469878</v>
       </c>
@@ -2712,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>4.2187131578947366</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>13.148536999999999</v>
+      </c>
       <c r="AD11" s="8">
         <v>19.080116666666665</v>
       </c>
@@ -2841,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>6.0443708609271525</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>12.987443000000001</v>
+      </c>
       <c r="AD12" s="8">
         <v>19.299787898089171</v>
       </c>
@@ -2892,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2928,25 +2983,59 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
+      <c r="O13" s="5">
+        <v>11613.440000000001</v>
+      </c>
+      <c r="P13" s="5">
+        <v>11613.440000000001</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.0015466713895023743</v>
+      </c>
+      <c r="R13" s="7">
+        <v>141</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.068181818181818121</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.35266000427091371</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.0038167674694147471</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.029496109679819246</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.026102627645211065</v>
+      </c>
+      <c r="X13" s="8">
+        <v>36.184913793103448</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>7.4361680272108845</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>9.7954025862068956</v>
+      </c>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="AD13" s="8">
+        <v>24.529454310344828</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.34482758620689657</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>0</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3065,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>4.4985116071428575</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>12.260266</v>
+      </c>
       <c r="AD14" s="8">
         <v>19.216071428571428</v>
       </c>
@@ -3194,7 +3285,9 @@
       <c r="AB15" s="8">
         <v>4.5748407643312099</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>14.267561000000001</v>
+      </c>
       <c r="AD15" s="8">
         <v>21.156856329113925</v>
       </c>
@@ -3323,7 +3416,9 @@
       <c r="AB16" s="8">
         <v>9.6039666666666665</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>14.649801</v>
+      </c>
       <c r="AD16" s="8">
         <v>21.26587142857143</v>
       </c>
@@ -3452,7 +3547,9 @@
       <c r="AB17" s="8">
         <v>5.3258426966292136</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>8.8914559999999998</v>
+      </c>
       <c r="AD17" s="8">
         <v>16.600000000000001</v>
       </c>
@@ -3581,7 +3678,9 @@
       <c r="AB18" s="8">
         <v>5.4424379629629636</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>9.7641039999999997</v>
+      </c>
       <c r="AD18" s="8">
         <v>16.507727272727273</v>
       </c>
@@ -3710,7 +3809,9 @@
       <c r="AB19" s="8">
         <v>6.3291659090909089</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>11.554166</v>
+      </c>
       <c r="AD19" s="8">
         <v>18.50075681818182</v>
       </c>
@@ -3839,7 +3940,9 @@
       <c r="AB20" s="8">
         <v>8.1318986754966893</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>15.090282999999999</v>
+      </c>
       <c r="AD20" s="8">
         <v>21.668817419354841</v>
       </c>
@@ -3968,7 +4071,9 @@
       <c r="AB21" s="8">
         <v>3.3584650793650797</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>8.3047609999999992</v>
+      </c>
       <c r="AD21" s="8">
         <v>14.265607936507937</v>
       </c>
@@ -4097,7 +4202,9 @@
       <c r="AB22" s="8">
         <v>4.7106796116504857</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>10.289408999999999</v>
+      </c>
       <c r="AD22" s="8">
         <v>16.972955660377359</v>
       </c>
@@ -4148,7 +4255,7 @@
         <v>19529</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C23" s="4">
         <v>44</v>
@@ -4184,25 +4291,61 @@
       <c t="s" r="N23" s="4">
         <v>52</v>
       </c>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="8"/>
-      <c r="AE23" s="6"/>
+      <c r="O23" s="5">
+        <v>24389.040000000001</v>
+      </c>
+      <c r="P23" s="5">
+        <v>24389.040000000001</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0.066245339638083323</v>
+      </c>
+      <c r="R23" s="7">
+        <v>265</v>
+      </c>
+      <c r="S23" s="6">
+        <v>0.011450381679389388</v>
+      </c>
+      <c r="T23" s="6">
+        <v>0.31423122025303168</v>
+      </c>
+      <c r="U23" s="6">
+        <v>-0.013935858073954531</v>
+      </c>
+      <c r="V23" s="6">
+        <v>0.01661215447594493</v>
+      </c>
+      <c r="W23" s="6">
+        <v>0.0063112160216228265</v>
+      </c>
+      <c r="X23" s="8">
+        <v>38.605379365079365</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>0.31216931216931215</v>
+      </c>
+      <c r="Z23" s="6">
+        <v>0.44973544973544971</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>10.29905303030303</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>8.8175722826086957</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>20.633004</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>27.203615343915342</v>
+      </c>
+      <c r="AE23" s="6">
+        <v>0.14814814814814814</v>
+      </c>
       <c r="AF23" s="9"/>
-      <c r="AG23" s="5"/>
+      <c r="AG23" s="5">
+        <v>-205.59999999999999</v>
+      </c>
       <c r="AH23" s="10">
         <v>2</v>
       </c>
@@ -4416,7 +4559,9 @@
       <c r="AB25" s="8">
         <v>12.768151485148515</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>36.358580000000003</v>
+      </c>
       <c r="AD25" s="8">
         <v>43.264851485148512</v>
       </c>
@@ -4545,7 +4690,9 @@
       <c r="AB26" s="8">
         <v>9.9055558139534892</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>15.979091</v>
+      </c>
       <c r="AD26" s="8">
         <v>22.344486466165414</v>
       </c>
@@ -4596,7 +4743,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4632,25 +4779,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>6558.0600000000004</v>
+      </c>
+      <c r="P27" s="5">
+        <v>6558.0600000000004</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.3868267123441369</v>
+      </c>
+      <c r="R27" s="7">
+        <v>64</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.46666666666666667</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.059476186555170278</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.31505835567225671</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.015840202742884328</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.003786333153402073</v>
+      </c>
+      <c r="X27" s="8">
+        <v>37.88774411764706</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>3.4310261538461537</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>9.9467741935483875</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>14.186970000000001</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>20.236869696969695</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.52941176470588236</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4691,7 +4874,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4727,25 +4910,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>9098.6499999999996</v>
+      </c>
+      <c r="P28" s="5">
+        <v>9098.6499999999996</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.16428741436099292</v>
+      </c>
+      <c r="R28" s="7">
+        <v>99</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.15116279069767447</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.0010011705033164261</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.31664595297104514</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.069520148593472664</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.061471701845878232</v>
+      </c>
+      <c r="X28" s="8">
+        <v>24.492398245614037</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.45614035087719296</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.2169970297029704</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>7.3137421052631586</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>9.2237989999999996</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>16.181578947368422</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.75438596491228072</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1104.8</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -4864,7 +5083,9 @@
       <c r="AB29" s="8">
         <v>23.680554761904762</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>35.375452000000003</v>
+      </c>
       <c r="AD29" s="8">
         <v>42.528029545454551</v>
       </c>
@@ -4989,7 +5210,9 @@
       <c r="AB30" s="8">
         <v>5.3120000000000003</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>7.999333</v>
+      </c>
       <c r="AD30" s="8">
         <v>14.969332</v>
       </c>
@@ -5120,7 +5343,9 @@
       <c r="AB31" s="8">
         <v>3.6796532467532468</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>10.582326999999999</v>
+      </c>
       <c r="AD31" s="8">
         <v>18.332911392405062</v>
       </c>
@@ -5249,7 +5474,9 @@
       <c r="AB32" s="8">
         <v>4.889120138888889</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.1978</v>
+      </c>
       <c r="AD32" s="8">
         <v>13.15914375</v>
       </c>
@@ -5300,7 +5527,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5334,25 +5561,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>13149.219999999999</v>
+      </c>
+      <c r="P33" s="5">
+        <v>13149.219999999999</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0.77831062640819426</v>
+      </c>
+      <c r="R33" s="7">
+        <v>104</v>
+      </c>
+      <c r="S33" s="6">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.33170936374933269</v>
+      </c>
+      <c r="U33" s="6">
+        <v>-0.0017362702882756545</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.014689920770965884</v>
+      </c>
+      <c r="W33" s="6">
+        <v>-0.0034046886431286418</v>
+      </c>
+      <c r="X33" s="8">
+        <v>25.508101388888889</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>2.4139423076923077</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>7.5018513888888885</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>10.003470999999999</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>16.962499999999999</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>0.81944444444444442</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5471,7 +5734,9 @@
       <c r="AB34" s="8">
         <v>1.0438230769230767</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="8">
+        <v>13.785513</v>
+      </c>
       <c r="AD34" s="8">
         <v>18.820787362637361</v>
       </c>
@@ -5524,7 +5789,7 @@
         <v>19561</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5560,25 +5825,61 @@
       <c t="s" r="N35" s="4">
         <v>52</v>
       </c>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
-      <c r="AD35" s="8"/>
-      <c r="AE35" s="6"/>
+      <c r="O35" s="5">
+        <v>3835.5</v>
+      </c>
+      <c r="P35" s="5">
+        <v>3835.5</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>-0.27221494848295102</v>
+      </c>
+      <c r="R35" s="7">
+        <v>43</v>
+      </c>
+      <c r="S35" s="6">
+        <v>-0.2321428571428571</v>
+      </c>
+      <c r="T35" s="6">
+        <v>2.4005147959848778</v>
+      </c>
+      <c r="U35" s="6">
+        <v>-0.0026060487550514924</v>
+      </c>
+      <c r="V35" s="6">
+        <v>0.21765845391735106</v>
+      </c>
+      <c r="W35" s="6">
+        <v>0.1460224221092426</v>
+      </c>
+      <c r="X35" s="8">
+        <v>90.83064516129032</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="Z35" s="6">
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="AA35" s="8">
+        <v>13.105184444444443</v>
+      </c>
+      <c r="AB35" s="8">
+        <v>22.681411538461536</v>
+      </c>
+      <c r="AC35" s="8">
+        <v>32.817267999999999</v>
+      </c>
+      <c r="AD35" s="8">
+        <v>34.098387096774189</v>
+      </c>
+      <c r="AE35" s="6">
+        <v>0.22580645161290322</v>
+      </c>
       <c r="AF35" s="9"/>
-      <c r="AG35" s="5"/>
+      <c r="AG35" s="5">
+        <v>0</v>
+      </c>
       <c r="AH35" s="10">
         <v>5</v>
       </c>
@@ -5794,7 +6095,9 @@
       <c r="AB37" s="8">
         <v>17.252816901408451</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>21.508918999999999</v>
+      </c>
       <c r="AD37" s="8">
         <v>28.446947887323944</v>
       </c>
@@ -5923,7 +6226,9 @@
       <c r="AB38" s="8">
         <v>3.4116666666666666</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>5.5191920000000003</v>
+      </c>
       <c r="AD38" s="8">
         <v>13.497223333333332</v>
       </c>
@@ -5974,7 +6279,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6010,25 +6315,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>10998.969999999999</v>
+      </c>
+      <c r="P39" s="5">
+        <v>10998.969999999999</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.19294556079657177</v>
+      </c>
+      <c r="R39" s="7">
+        <v>122</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.042735042735042805</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.33872358048071771</v>
+      </c>
+      <c r="U39" s="6">
+        <v>0.0087517740297500587</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.046453622475559078</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.024717041686630661</v>
+      </c>
+      <c r="X39" s="8">
+        <v>44.086708860759494</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.77215189873417722</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.53164556962025311</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>6.0071233870967742</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>22.620601388888886</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>28.540279000000002</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>33.739662025316456</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.29113924050632911</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6147,7 +6488,9 @@
       <c r="AB40" s="8">
         <v>8.4887389189189193</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>12.648720000000001</v>
+      </c>
       <c r="AD40" s="8">
         <v>19.131849738219895</v>
       </c>
@@ -6276,7 +6619,9 @@
       <c r="AB41" s="8">
         <v>8.2996172413793108</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>11.780775</v>
+      </c>
       <c r="AD41" s="8">
         <v>17.189743956043955</v>
       </c>
@@ -6422,7 +6767,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6458,25 +6803,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>11800.51</v>
+      </c>
+      <c r="P43" s="5">
+        <v>11800.51</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0.14971462977866024</v>
+      </c>
+      <c r="R43" s="7">
+        <v>105</v>
+      </c>
+      <c r="S43" s="6">
+        <v>0.050000000000000044</v>
+      </c>
+      <c r="T43" s="6">
+        <v>0.30291233175515297</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.038871201329434064</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.014891178432118611</v>
+      </c>
+      <c r="W43" s="6">
+        <v>-0.00062086299659929952</v>
+      </c>
+      <c r="X43" s="8">
+        <v>82.014236458333329</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.092783505154639179</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>25.453655263157895</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>29.710763541666665</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>56.480522000000001</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>63.154513541666667</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.010416666666666666</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6595,7 +6976,9 @@
       <c r="AB44" s="8">
         <v>28.408695652173911</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>35.548479</v>
+      </c>
       <c r="AD44" s="8">
         <v>43.119712903225803</v>
       </c>
@@ -6724,7 +7107,9 @@
       <c r="AB45" s="8">
         <v>2.9125000000000001</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>7.4691169999999998</v>
+      </c>
       <c r="AD45" s="8">
         <v>13.368852459016393</v>
       </c>
@@ -6849,7 +7234,9 @@
       <c r="AB46" s="8">
         <v>8.3538283783783793</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>13.767116</v>
+      </c>
       <c r="AD46" s="8">
         <v>20.714639189189189</v>
       </c>
@@ -6978,7 +7365,9 @@
       <c r="AB47" s="8">
         <v>8.7464907894736843</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>13.980668</v>
+      </c>
       <c r="AD47" s="8">
         <v>20.586111538461537</v>
       </c>
@@ -7105,7 +7494,9 @@
       <c r="AB48" s="8">
         <v>6.5875711864406776</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>14.40507</v>
+      </c>
       <c r="AD48" s="8">
         <v>21.3613</v>
       </c>
@@ -7232,7 +7623,9 @@
       <c r="AB49" s="8">
         <v>8.9662966666666666</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>15.935317</v>
+      </c>
       <c r="AD49" s="8">
         <v>23.504709782608696</v>
       </c>
@@ -7283,7 +7676,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7319,25 +7712,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>6886.75</v>
+      </c>
+      <c r="P50" s="5">
+        <v>6886.75</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.18049904862088706</v>
+      </c>
+      <c r="R50" s="7">
+        <v>80</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.2592592592592593</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.25651458235016517</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.052862119287036699</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.047997676698007044</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.010779830834573638</v>
+      </c>
+      <c r="X50" s="8">
+        <v>24.692592592592593</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>4.0895294871794867</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>5.7360000000000007</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>9.9187480000000008</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>16.99043148148148</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7551,7 +7980,9 @@
       <c r="AB52" s="8">
         <v>2.6383848484848484</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>6.8041229999999997</v>
+      </c>
       <c r="AD52" s="8">
         <v>14.256944444444445</v>
       </c>
@@ -7678,7 +8109,9 @@
       <c r="AB53" s="8">
         <v>2.624536111111111</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>6.3574070000000003</v>
+      </c>
       <c r="AD53" s="8">
         <v>13.293055555555556</v>
       </c>
@@ -7807,7 +8240,9 @@
       <c r="AB54" s="8">
         <v>14.298957812499999</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>20.363019999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>27.274479687500001</v>
       </c>
@@ -7858,7 +8293,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7894,25 +8329,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>11487.33</v>
+      </c>
+      <c r="P55" s="5">
+        <v>11487.33</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.44111145680177044</v>
+      </c>
+      <c r="R55" s="7">
+        <v>126</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.35483870967741926</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.31151538259978601</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.07655295007630146</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.051729949431242948</v>
+      </c>
+      <c r="X55" s="8">
+        <v>25.795999999999999</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>4.2543259541984728</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>4.9893329999999994</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>9.3317270000000008</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>16.285667</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.79000000000000004</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8029,7 +8500,9 @@
       <c r="AB56" s="8">
         <v>4.8468669172932328</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>15.906743000000001</v>
+      </c>
       <c r="AD56" s="8">
         <v>24.263703703703705</v>
       </c>
@@ -8158,7 +8631,9 @@
       <c r="AB57" s="8">
         <v>6.0232809523809525</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>11.688230000000001</v>
+      </c>
       <c r="AD57" s="8">
         <v>18.108333333333334</v>
       </c>
@@ -8382,7 +8857,9 @@
       <c r="AB59" s="8">
         <v>5.1186878787878785</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>9.7413709999999991</v>
+      </c>
       <c r="AD59" s="8">
         <v>15.920833333333333</v>
       </c>
@@ -8511,7 +8988,9 @@
       <c r="AB60" s="8">
         <v>3.1621212121212121</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>7.2260090000000003</v>
+      </c>
       <c r="AD60" s="8">
         <v>14.787500000000001</v>
       </c>
@@ -8638,7 +9117,9 @@
       <c r="AB61" s="8">
         <v>4.5494781250000003</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>7.143923</v>
+      </c>
       <c r="AD61" s="8">
         <v>13.883333333333333</v>
       </c>
@@ -8765,7 +9246,9 @@
       <c r="AB62" s="8">
         <v>4.3142857142857141</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>7.869046</v>
+      </c>
       <c r="AD62" s="8">
         <v>14.053332857142857</v>
       </c>
@@ -8894,7 +9377,9 @@
       <c r="AB63" s="8">
         <v>10.415045833333332</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>14.133267999999999</v>
+      </c>
       <c r="AD63" s="8">
         <v>19.523555999999999</v>
       </c>
@@ -9021,7 +9506,9 @@
       <c r="AB64" s="8">
         <v>11.571837931034484</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>15.483665999999999</v>
+      </c>
       <c r="AD64" s="8">
         <v>22.223562068965517</v>
       </c>
@@ -9217,10 +9704,10 @@
         <v>0.25</v>
       </c>
       <c r="T66" s="6">
-        <v>0.33376298686549</v>
+        <v>0.3296743698780436</v>
       </c>
       <c r="U66" s="6">
-        <v>-0.018233896424456265</v>
+        <v>-0.022322513411902695</v>
       </c>
       <c r="V66" s="6">
         <v>0.037018709896793393</v>
@@ -9243,7 +9730,9 @@
       <c r="AB66" s="8">
         <v>5.2137254901960777</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>10.413098</v>
+      </c>
       <c r="AD66" s="8">
         <v>17.252941176470589</v>
       </c>
@@ -9370,7 +9859,9 @@
       <c r="AB67" s="8">
         <v>11.52340425531915</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>20.168890000000001</v>
+      </c>
       <c r="AD67" s="8">
         <v>26.696527083333333</v>
       </c>
@@ -9499,7 +9990,9 @@
       <c r="AB68" s="8">
         <v>2.6410560975609756</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>6.0569090000000001</v>
+      </c>
       <c r="AD68" s="8">
         <v>13.009348780487803</v>
       </c>
@@ -9626,7 +10119,9 @@
       <c r="AB69" s="8">
         <v>13.235227272727274</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>35.165298999999997</v>
+      </c>
       <c r="AD69" s="8">
         <v>42.345184444444449</v>
       </c>
@@ -9677,7 +10172,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -9713,25 +10208,61 @@
       <c t="s" r="N70" s="4">
         <v>52</v>
       </c>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-      <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="6"/>
+      <c r="O70" s="5">
+        <v>8065.1700000000001</v>
+      </c>
+      <c r="P70" s="5">
+        <v>8065.1700000000001</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>-0.034763345476827578</v>
+      </c>
+      <c r="R70" s="7">
+        <v>91</v>
+      </c>
+      <c r="S70" s="6">
+        <v>0</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0.35971846842657995</v>
+      </c>
+      <c r="U70" s="6">
+        <v>0.00079980955144156902</v>
+      </c>
+      <c r="V70" s="6">
+        <v>0.011669437841979772</v>
+      </c>
+      <c r="W70" s="6">
+        <v>-0.0015912869784517872</v>
+      </c>
+      <c r="X70" s="8">
+        <v>25.940000000000001</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="6">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="AA70" s="8">
+        <v>4.5675824175824173</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>7.0194437499999998</v>
+      </c>
+      <c r="AC70" s="8">
+        <v>11.637444</v>
+      </c>
+      <c r="AD70" s="8">
+        <v>18.218333999999999</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>0.78000000000000003</v>
+      </c>
       <c r="AF70" s="9"/>
-      <c r="AG70" s="5"/>
+      <c r="AG70" s="5">
+        <v>-79.599999999999994</v>
+      </c>
       <c r="AH70" s="10">
         <v>2</v>
       </c>
@@ -9772,7 +10303,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9806,25 +10337,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>7864.9700000000003</v>
+      </c>
+      <c r="P71" s="5">
+        <v>7864.9700000000003</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.038400547740874535</v>
+      </c>
+      <c r="R71" s="7">
+        <v>97</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.10185185185185186</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.28794716318053343</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.03018501024161567</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.054649858804292961</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.015636359706394303</v>
+      </c>
+      <c r="X71" s="8">
+        <v>23.018517777777777</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.5145833333333334</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.6511627906976747</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>7.2855590000000001</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>14.70926</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.82222222222222219</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-349.18000000000001</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9941,7 +10508,9 @@
       <c r="AB72" s="8">
         <v>4.2196076470588233</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>11.803036000000001</v>
+      </c>
       <c r="AD72" s="8">
         <v>18.644864534883723</v>
       </c>
@@ -10068,7 +10637,9 @@
       <c r="AB73" s="8">
         <v>3.3820184210526314</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>6.7873010000000003</v>
+      </c>
       <c r="AD73" s="8">
         <v>14.342917499999999</v>
       </c>
@@ -10210,7 +10781,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10246,25 +10817,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>6571.1499999999996</v>
+      </c>
+      <c r="P75" s="5">
+        <v>6571.1499999999996</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.087616527218147944</v>
+      </c>
+      <c r="R75" s="7">
+        <v>72</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.18181818181818177</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.30192432070489944</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.045083661155201148</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.024242560282446757</v>
+      </c>
+      <c r="X75" s="8">
+        <v>29.130832500000004</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.9769957746478868</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>11.074999999999999</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>16.687601000000001</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>23.579167500000001</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-69.799999999999997</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10476,7 +11083,9 @@
       <c r="AB77" s="8">
         <v>3.0238107142857147</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>4.45357</v>
+      </c>
       <c r="AD77" s="8">
         <v>11.047127586206896</v>
       </c>
@@ -10601,7 +11210,9 @@
       <c r="AB78" s="8">
         <v>5.6433330000000002</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>8.1874990000000007</v>
+      </c>
       <c r="AD78" s="8">
         <v>16.155833000000001</v>
       </c>
@@ -10730,7 +11341,9 @@
       <c r="AB79" s="8">
         <v>11.893790196078431</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>16.137059000000001</v>
+      </c>
       <c r="AD79" s="8">
         <v>23.080064705882354</v>
       </c>
@@ -10857,7 +11470,9 @@
       <c r="AB80" s="8">
         <v>8.6681074074074083</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>13.512027</v>
+      </c>
       <c r="AD80" s="8">
         <v>22.925097647058823</v>
       </c>
@@ -10988,7 +11603,9 @@
       <c r="AB81" s="8">
         <v>4.6177062500000003</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>8.530208</v>
+      </c>
       <c r="AD81" s="8">
         <v>15.476043750000001</v>
       </c>
@@ -11117,7 +11734,9 @@
       <c r="AB82" s="8">
         <v>10.677949230769229</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>16.110254999999999</v>
+      </c>
       <c r="AD82" s="8">
         <v>22.964615384615385</v>
       </c>
@@ -11339,7 +11958,9 @@
       <c r="AB84" s="8">
         <v>7.4727272727272727</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>13.630364999999999</v>
+      </c>
       <c r="AD84" s="8">
         <v>19.705902083333331</v>
       </c>
@@ -11468,7 +12089,9 @@
       <c r="AB85" s="8">
         <v>28.629764285714288</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>32.429205000000003</v>
+      </c>
       <c r="AD85" s="8">
         <v>28.769842857142855</v>
       </c>
@@ -11597,7 +12220,9 @@
       <c r="AB86" s="8">
         <v>4.1146551724137934</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>19.59891</v>
+      </c>
       <c r="AD86" s="8">
         <v>27.974425862068962</v>
       </c>
@@ -11726,7 +12351,9 @@
       <c r="AB87" s="8">
         <v>8.1184535714285708</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>12.542063000000001</v>
+      </c>
       <c r="AD87" s="8">
         <v>16.806019444444445</v>
       </c>
@@ -11853,7 +12480,9 @@
       <c r="AB88" s="8">
         <v>4.9778918367346936</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>7.0377539999999996</v>
+      </c>
       <c r="AD88" s="8">
         <v>13.062334</v>
       </c>
@@ -11997,7 +12626,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12033,25 +12662,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>6459.29</v>
+      </c>
+      <c r="P90" s="5">
+        <v>6459.29</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>-0.10883358880152538</v>
+      </c>
+      <c r="R90" s="7">
+        <v>72</v>
+      </c>
+      <c r="S90" s="6">
+        <v>-0.15294117647058825</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0.021670183565066746</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-3.4298732523233975</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.10698296562006041</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.074552156661181021</v>
+      </c>
+      <c r="X90" s="8">
+        <v>29.458175471698116</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.43396226415094341</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.16981132075471697</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>8.6434782608695642</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>8.6195519230769229</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>17.553197999999998</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>24.229245283018869</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.62264150943396224</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-130.75999999999999</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12170,7 +12835,9 @@
       <c r="AB91" s="8">
         <v>3.7544265625</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>9.7979160000000007</v>
+      </c>
       <c r="AD91" s="8">
         <v>16.734635937499998</v>
       </c>
@@ -12299,7 +12966,9 @@
       <c r="AB92" s="8">
         <v>4.7100999999999997</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>12.328787</v>
+      </c>
       <c r="AD92" s="8">
         <v>20.245454545454546</v>
       </c>
@@ -12426,7 +13095,9 @@
       <c r="AB93" s="8">
         <v>1.8597345132743364</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>3.219821</v>
+      </c>
       <c r="AD93" s="8">
         <v>10.138304385964911</v>
       </c>
@@ -12553,7 +13224,9 @@
       <c r="AB94" s="8">
         <v>1.9958333333333333</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>5.552295</v>
+      </c>
       <c r="AD94" s="8">
         <v>13.413944897959185</v>
       </c>
@@ -12775,7 +13448,9 @@
       <c r="AB96" s="8">
         <v>3.4854757142857147</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>5.8090469999999996</v>
+      </c>
       <c r="AD96" s="8">
         <v>12.751428571428571</v>
       </c>
@@ -12904,7 +13579,9 @@
       <c r="AB97" s="8">
         <v>1.7697537037037037</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>7.410056</v>
+      </c>
       <c r="AD97" s="8">
         <v>13.303636363636365</v>
       </c>
@@ -13033,7 +13710,9 @@
       <c r="AB98" s="8">
         <v>12.324329885057471</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>19.528635999999999</v>
+      </c>
       <c r="AD98" s="8">
         <v>26.275568181818183</v>
       </c>
@@ -13162,7 +13841,9 @@
       <c r="AB99" s="8">
         <v>5.5509359550561799</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>11.551302</v>
+      </c>
       <c r="AD99" s="8">
         <v>18.469999999999999</v>
       </c>
@@ -13291,7 +13972,9 @@
       <c r="AB100" s="8">
         <v>4.6759697674418605</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>13.98527</v>
+      </c>
       <c r="AD100" s="8">
         <v>22.943023255813952</v>
       </c>
@@ -13418,7 +14101,9 @@
       <c r="AB101" s="8">
         <v>21.015671641791045</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>25.903569999999998</v>
+      </c>
       <c r="AD101" s="8">
         <v>30.802283561643833</v>
       </c>
@@ -13642,7 +14327,9 @@
       <c r="AB103" s="8">
         <v>5.1247469696969699</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>10.732345</v>
+      </c>
       <c r="AD103" s="8">
         <v>16.596765671641794</v>
       </c>
@@ -13771,7 +14458,9 @@
       <c r="AB104" s="8">
         <v>4.2695912280701753</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>10.162245</v>
+      </c>
       <c r="AD104" s="8">
         <v>18.403954237288136</v>
       </c>
@@ -13898,7 +14587,9 @@
       <c r="AB105" s="8">
         <v>10.914634146341463</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>15.391463</v>
+      </c>
       <c r="AD105" s="8">
         <v>21.639431707317073</v>
       </c>
@@ -14027,7 +14718,9 @@
       <c r="AB106" s="8">
         <v>5.1055541666666668</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>9.64236</v>
+      </c>
       <c r="AD106" s="8">
         <v>16.612500000000001</v>
       </c>
@@ -14156,7 +14849,9 @@
       <c r="AB107" s="8">
         <v>19.068611666666666</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>29.433664</v>
+      </c>
       <c r="AD107" s="8">
         <v>35.701343548387094</v>
       </c>
@@ -14300,7 +14995,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14334,25 +15029,61 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="O109" s="5">
+        <v>12668.959999999999</v>
+      </c>
+      <c r="P109" s="5">
+        <v>12668.959999999999</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>0.31643065259587777</v>
+      </c>
+      <c r="R109" s="7">
+        <v>128</v>
+      </c>
+      <c r="S109" s="6">
+        <v>0.26732673267326734</v>
+      </c>
+      <c r="T109" s="6">
+        <v>-0.12453271618191233</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.44982934668670516</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.012147879541809275</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.0010317342544297243</v>
+      </c>
+      <c r="X109" s="8">
+        <v>36.81111111111111</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>5.6462823076923074</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>16.716357407407408</v>
+      </c>
+      <c r="AC109" s="8">
+        <v>22.195678000000001</v>
+      </c>
+      <c r="AD109" s="8">
+        <v>30.123457407407408</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14784,7 +15515,9 @@
       <c r="AB113" s="8">
         <v>3.1053677966101696</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>5.3782160000000001</v>
+      </c>
       <c r="AD113" s="8">
         <v>14.914480327868853</v>
       </c>
@@ -14835,7 +15568,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>44</v>
@@ -14871,25 +15604,61 @@
       <c t="s" r="N114" s="4">
         <v>52</v>
       </c>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-      <c r="V114" s="6"/>
-      <c r="W114" s="6"/>
-      <c r="X114" s="8"/>
-      <c r="Y114" s="6"/>
-      <c r="Z114" s="6"/>
-      <c r="AA114" s="8"/>
-      <c r="AB114" s="8"/>
-      <c r="AC114" s="8"/>
-      <c r="AD114" s="8"/>
-      <c r="AE114" s="6"/>
+      <c r="O114" s="5">
+        <v>11264.969999999999</v>
+      </c>
+      <c r="P114" s="5">
+        <v>11264.969999999999</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>0.43680527123358948</v>
+      </c>
+      <c r="R114" s="7">
+        <v>94</v>
+      </c>
+      <c r="S114" s="6">
+        <v>0.22077922077922074</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0.028547852324506861</v>
+      </c>
+      <c r="U114" s="6">
+        <v>-0.25131884949538258</v>
+      </c>
+      <c r="V114" s="6">
+        <v>0.020304847682683577</v>
+      </c>
+      <c r="W114" s="6">
+        <v>0.01276998518415939</v>
+      </c>
+      <c r="X114" s="8">
+        <v>24.531798684210525</v>
+      </c>
+      <c r="Y114" s="6">
+        <v>0.86842105263157898</v>
+      </c>
+      <c r="Z114" s="6">
+        <v>0.039473684210526314</v>
+      </c>
+      <c r="AA114" s="8">
+        <v>4.2166663157894737</v>
+      </c>
+      <c r="AB114" s="8">
+        <v>3.0481739726027395</v>
+      </c>
+      <c r="AC114" s="8">
+        <v>7.168647</v>
+      </c>
+      <c r="AD114" s="8">
+        <v>14.94188552631579</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF114" s="9"/>
-      <c r="AG114" s="5"/>
+      <c r="AG114" s="5">
+        <v>-429.60000000000002</v>
+      </c>
       <c r="AH114" s="10">
         <v>2</v>
       </c>
@@ -15008,7 +15777,9 @@
       <c r="AB115" s="8">
         <v>7.8271921052631575</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>11.469072000000001</v>
+      </c>
       <c r="AD115" s="8">
         <v>19.190597435897438</v>
       </c>
@@ -15230,7 +16001,9 @@
       <c r="AB117" s="8">
         <v>7.008333928571429</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>10.75614</v>
+      </c>
       <c r="AD117" s="8">
         <v>14.703947368421053</v>
       </c>
@@ -15281,7 +16054,7 @@
         <v>19746</v>
       </c>
       <c r="B118" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C118" s="4">
         <v>44</v>
@@ -15317,25 +16090,61 @@
       <c t="s" r="N118" s="4">
         <v>52</v>
       </c>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
-      <c r="V118" s="6"/>
-      <c r="W118" s="6"/>
-      <c r="X118" s="8"/>
-      <c r="Y118" s="6"/>
-      <c r="Z118" s="6"/>
-      <c r="AA118" s="8"/>
-      <c r="AB118" s="8"/>
-      <c r="AC118" s="8"/>
-      <c r="AD118" s="8"/>
-      <c r="AE118" s="6"/>
+      <c r="O118" s="5">
+        <v>9592.1100000000006</v>
+      </c>
+      <c r="P118" s="5">
+        <v>9592.1100000000006</v>
+      </c>
+      <c r="Q118" s="6">
+        <v>0.29448702221466494</v>
+      </c>
+      <c r="R118" s="7">
+        <v>112</v>
+      </c>
+      <c r="S118" s="6">
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0.29041343354069121</v>
+      </c>
+      <c r="U118" s="6">
+        <v>-0.057825900662106668</v>
+      </c>
+      <c r="V118" s="6">
+        <v>0.032765835671192262</v>
+      </c>
+      <c r="W118" s="6">
+        <v>0.0076973158147685961</v>
+      </c>
+      <c r="X118" s="8">
+        <v>26.474603174603175</v>
+      </c>
+      <c r="Y118" s="6">
+        <v>0.36507936507936506</v>
+      </c>
+      <c r="Z118" s="6">
+        <v>0.12698412698412698</v>
+      </c>
+      <c r="AA118" s="8">
+        <v>7.982679411764706</v>
+      </c>
+      <c r="AB118" s="8">
+        <v>9.6658051724137941</v>
+      </c>
+      <c r="AC118" s="8">
+        <v>17.311432</v>
+      </c>
+      <c r="AD118" s="8">
+        <v>22.75873015873016</v>
+      </c>
+      <c r="AE118" s="6">
+        <v>0.65079365079365081</v>
+      </c>
       <c r="AF118" s="9"/>
-      <c r="AG118" s="5"/>
+      <c r="AG118" s="5">
+        <v>-248.80000000000001</v>
+      </c>
       <c r="AH118" s="10">
         <v>2</v>
       </c>
@@ -15454,7 +16263,9 @@
       <c r="AB119" s="8">
         <v>8.2076581081081095</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>13.620945000000001</v>
+      </c>
       <c r="AD119" s="8">
         <v>20.567793243243241</v>
       </c>
@@ -15581,7 +16392,9 @@
       <c r="AB120" s="8">
         <v>10.910294117647059</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>17.993627</v>
+      </c>
       <c r="AD120" s="8">
         <v>25.939214705882353</v>
       </c>
@@ -15708,7 +16521,9 @@
       <c r="AB121" s="8">
         <v>3.4111166666666666</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>9.9846400000000006</v>
+      </c>
       <c r="AD121" s="8">
         <v>12.664705882352942</v>
       </c>
@@ -15837,7 +16652,9 @@
       <c r="AB122" s="8">
         <v>1.2553677966101695</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>5.158366</v>
+      </c>
       <c r="AD122" s="8">
         <v>12.067513559322034</v>
       </c>
@@ -15888,7 +16705,7 @@
         <v>19754</v>
       </c>
       <c r="B123" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C123" s="4">
         <v>44</v>
@@ -15924,25 +16741,61 @@
       <c t="s" r="N123" s="4">
         <v>52</v>
       </c>
-      <c r="O123" s="5"/>
-      <c r="P123" s="5"/>
-      <c r="Q123" s="6"/>
-      <c r="R123" s="7"/>
-      <c r="S123" s="6"/>
-      <c r="T123" s="6"/>
-      <c r="U123" s="6"/>
-      <c r="V123" s="6"/>
-      <c r="W123" s="6"/>
-      <c r="X123" s="8"/>
-      <c r="Y123" s="6"/>
-      <c r="Z123" s="6"/>
-      <c r="AA123" s="8"/>
-      <c r="AB123" s="8"/>
-      <c r="AC123" s="8"/>
-      <c r="AD123" s="8"/>
-      <c r="AE123" s="6"/>
+      <c r="O123" s="5">
+        <v>11861.309999999999</v>
+      </c>
+      <c r="P123" s="5">
+        <v>11861.309999999999</v>
+      </c>
+      <c r="Q123" s="6">
+        <v>-0.26525192695205535</v>
+      </c>
+      <c r="R123" s="7">
+        <v>110</v>
+      </c>
+      <c r="S123" s="6">
+        <v>-0.27631578947368418</v>
+      </c>
+      <c r="T123" s="6">
+        <v>0.30030311997578685</v>
+      </c>
+      <c r="U123" s="6">
+        <v>-0.023820438046050565</v>
+      </c>
+      <c r="V123" s="6">
+        <v>0.014375772996405963</v>
+      </c>
+      <c r="W123" s="6">
+        <v>-0.0049180486809635698</v>
+      </c>
+      <c r="X123" s="8">
+        <v>23.713492063492065</v>
+      </c>
+      <c r="Y123" s="6">
+        <v>0.87301587301587302</v>
+      </c>
+      <c r="Z123" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="8">
+        <v>3.606907207207207</v>
+      </c>
+      <c r="AB123" s="8">
+        <v>5.5084650793650791</v>
+      </c>
+      <c r="AC123" s="8">
+        <v>9.3164010000000008</v>
+      </c>
+      <c r="AD123" s="8">
+        <v>17.264020634920634</v>
+      </c>
+      <c r="AE123" s="6">
+        <v>0.82539682539682535</v>
+      </c>
       <c r="AF123" s="9"/>
-      <c r="AG123" s="5"/>
+      <c r="AG123" s="5">
+        <v>0</v>
+      </c>
       <c r="AH123" s="10">
         <v>4</v>
       </c>
@@ -16061,7 +16914,9 @@
       <c r="AB124" s="8">
         <v>4.9773785714285719</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>9.1573799999999999</v>
+      </c>
       <c r="AD124" s="8">
         <v>16.826192857142857</v>
       </c>
@@ -16190,7 +17045,9 @@
       <c r="AB125" s="8">
         <v>6.7359756097560979</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>10.640243</v>
+      </c>
       <c r="AD125" s="8">
         <v>18.584756097560977</v>
       </c>
@@ -16319,7 +17176,9 @@
       <c r="AB126" s="8">
         <v>17.570721621621622</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>20.897746999999999</v>
+      </c>
       <c r="AD126" s="8">
         <v>27.819818918918919</v>
       </c>
@@ -16448,7 +17307,9 @@
       <c r="AB127" s="8">
         <v>6.9699999999999998</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>13.949687000000001</v>
+      </c>
       <c r="AD127" s="8">
         <v>23.418280645161289</v>
       </c>
@@ -16577,7 +17438,9 @@
       <c r="AB128" s="8">
         <v>5.146668</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>13.027915999999999</v>
+      </c>
       <c r="AD128" s="8">
         <v>20.565999999999999</v>
       </c>
@@ -16706,7 +17569,9 @@
       <c r="AB129" s="8">
         <v>19.57909661016949</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>28.819773000000001</v>
+      </c>
       <c r="AD129" s="8">
         <v>35.722316949152543</v>
       </c>
@@ -16835,7 +17700,9 @@
       <c r="AB130" s="8">
         <v>6.2685185185185182</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>8.7893509999999999</v>
+      </c>
       <c r="AD130" s="8">
         <v>15.345239285714285</v>
       </c>
@@ -16962,7 +17829,9 @@
       <c r="AB131" s="8">
         <v>5.2986083333333331</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>12.57938</v>
+      </c>
       <c r="AD131" s="8">
         <v>18.970515384615386</v>
       </c>
@@ -17074,7 +17943,7 @@
         <v>0.015415688728384806</v>
       </c>
       <c r="W132" s="6">
-        <v>-0.016906995666816874</v>
+        <v>-0.016741128791713206</v>
       </c>
       <c r="X132" s="8">
         <v>25.247482014388488</v>
@@ -17091,7 +17960,9 @@
       <c r="AB132" s="8">
         <v>7.2995131386861321</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>12.104513000000001</v>
+      </c>
       <c r="AD132" s="8">
         <v>17.857793525179854</v>
       </c>
@@ -17220,7 +18091,9 @@
       <c r="AB133" s="8">
         <v>16.882000000000001</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>21.044796999999999</v>
+      </c>
       <c r="AD133" s="8">
         <v>26.366975925925928</v>
       </c>
@@ -17349,7 +18222,9 @@
       <c r="AB134" s="8">
         <v>17.31846756756757</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>31.775046</v>
+      </c>
       <c r="AD134" s="8">
         <v>38.538157894736841</v>
       </c>
@@ -17478,7 +18353,9 @@
       <c r="AB135" s="8">
         <v>3.4238729729729731</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>6.7716200000000004</v>
+      </c>
       <c r="AD135" s="8">
         <v>13.725675675675676</v>
       </c>
@@ -17529,7 +18406,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -17565,25 +18442,61 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>6824.3599999999997</v>
+      </c>
+      <c r="P136" s="5">
+        <v>6824.3599999999997</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>-0.1272103153592139</v>
+      </c>
+      <c r="R136" s="7">
+        <v>66</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.18248505354348246</v>
+      </c>
+      <c r="U136" s="6">
+        <v>-0.088589450146240811</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.0097778399732722197</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.0057005345556213338</v>
+      </c>
+      <c r="X136" s="8">
+        <v>26.448275862068964</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>7.3118681818181823</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>8.1929499999999997</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>14.749269</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>20.206320689655172</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.65517241379310343</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-73.799999999999997</v>
+      </c>
       <c r="AH136" s="10">
         <v>4</v>
       </c>
@@ -17700,7 +18613,9 @@
       <c r="AB137" s="8">
         <v>7.2302999999999997</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>15.88308</v>
+      </c>
       <c r="AD137" s="8">
         <v>19.972727272727273</v>
       </c>
@@ -17827,7 +18742,9 @@
       <c r="AB138" s="8">
         <v>15.576347305389222</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>25.409780999999999</v>
+      </c>
       <c r="AD138" s="8">
         <v>30.792571428571428</v>
       </c>
@@ -17956,7 +18873,9 @@
       <c r="AB139" s="8">
         <v>3.5994241379310346</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>5.7309060000000001</v>
+      </c>
       <c r="AD139" s="8">
         <v>10.682408333333335</v>
       </c>
@@ -18273,7 +19192,9 @@
       <c r="AB142" s="8">
         <v>3.9916674999999997</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>7.869999</v>
+      </c>
       <c r="AD142" s="8">
         <v>16.707917500000001</v>
       </c>
@@ -18400,7 +19321,9 @@
       <c r="AB143" s="8">
         <v>7.9493150684931502</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>13.192736</v>
+      </c>
       <c r="AD143" s="8">
         <v>20.861110666666665</v>
       </c>
@@ -18529,7 +19452,9 @@
       <c r="AB144" s="8">
         <v>1.5926583333333333</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>4.3312229999999996</v>
+      </c>
       <c r="AD144" s="8">
         <v>11.280158333333334</v>
       </c>
@@ -18658,7 +19583,9 @@
       <c r="AB145" s="8">
         <v>4.5774783783783786</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>9.8276959999999995</v>
+      </c>
       <c r="AD145" s="8">
         <v>12.548464473684211</v>
       </c>
@@ -18787,7 +19714,9 @@
       <c r="AB146" s="8">
         <v>3.0639875000000001</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>7.0546309999999997</v>
+      </c>
       <c r="AD146" s="8">
         <v>12.904464285714285</v>
       </c>
@@ -18916,7 +19845,9 @@
       <c r="AB147" s="8">
         <v>2.6574324324324325</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>7.0119360000000004</v>
+      </c>
       <c r="AD147" s="8">
         <v>13.961036486486487</v>
       </c>
@@ -19047,7 +19978,9 @@
       <c r="AB148" s="8">
         <v>14.711051086956521</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>25.575766000000002</v>
+      </c>
       <c r="AD148" s="8">
         <v>33.27114731182796</v>
       </c>
@@ -19176,7 +20109,9 @@
       <c r="AB149" s="8">
         <v>10.737442465753425</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>16.979219000000001</v>
+      </c>
       <c r="AD149" s="8">
         <v>24.027853424657536</v>
       </c>
@@ -19303,7 +20238,9 @@
       <c r="AB150" s="8">
         <v>3.8739771929824562</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>10.228698</v>
+      </c>
       <c r="AD150" s="8">
         <v>16.758611666666667</v>
       </c>
@@ -19434,7 +20371,9 @@
       <c r="AB151" s="8">
         <v>2.3226770491803279</v>
       </c>
-      <c r="AC151" s="8"/>
+      <c r="AC151" s="8">
+        <v>7.6868840000000001</v>
+      </c>
       <c r="AD151" s="8">
         <v>14.639618032786885</v>
       </c>
@@ -19565,7 +20504,9 @@
       <c r="AB152" s="8">
         <v>4.3094827586206899</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>8.2663779999999996</v>
+      </c>
       <c r="AD152" s="8">
         <v>15.213505172413793</v>
       </c>
@@ -19694,7 +20635,9 @@
       <c r="AB153" s="8">
         <v>9.9847082474226809</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>15.407522</v>
+      </c>
       <c r="AD153" s="8">
         <v>22.165696116504854</v>
       </c>
@@ -19706,7 +20649,7 @@
         <v>-4781.3699999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -19819,7 +20762,9 @@
       <c r="AB154" s="8">
         <v>19.001666666666665</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>21.002220999999999</v>
+      </c>
       <c r="AD154" s="8">
         <v>29.939443333333333</v>
       </c>
@@ -19946,7 +20891,9 @@
       <c r="AB155" s="8">
         <v>2.6887983606557375</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>5.369173</v>
+      </c>
       <c r="AD155" s="8">
         <v>11.35268870967742</v>
       </c>
@@ -20075,7 +21022,9 @@
       <c r="AB156" s="8">
         <v>4.6961982456140348</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>18.980875000000001</v>
+      </c>
       <c r="AD156" s="8">
         <v>25.264246774193548</v>
       </c>
@@ -20316,7 +21265,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -20352,25 +21301,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="O159" s="5">
+        <v>17405.02</v>
+      </c>
+      <c r="P159" s="5">
+        <v>17405.02</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0.16890900384621332</v>
+      </c>
+      <c r="R159" s="7">
+        <v>176</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.20547945205479445</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.28528305626767447</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.0012808201312035263</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.026550156219297651</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.0079405826594855962</v>
+      </c>
+      <c r="X159" s="8">
+        <v>41.751524836601305</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>10.397113407821228</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>6.9014163398692814</v>
+      </c>
+      <c r="AC159" s="8">
+        <v>18.009371999999999</v>
+      </c>
+      <c r="AD159" s="8">
+        <v>24.831154901960787</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.24183006535947713</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-29.899999999999999</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>
@@ -20485,7 +21470,9 @@
       <c r="AB160" s="8">
         <v>7.0318847826086959</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>12.112318</v>
+      </c>
       <c r="AD160" s="8">
         <v>19.05108695652174</v>
       </c>
@@ -20729,7 +21716,9 @@
       <c r="AB162" s="8">
         <v>8.7818847826086959</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>22.288346000000001</v>
+      </c>
       <c r="AD162" s="8">
         <v>29.462244897959184</v>
       </c>
@@ -20858,7 +21847,9 @@
       <c r="AB163" s="8">
         <v>8.3187022900763363</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>13.544654</v>
+      </c>
       <c r="AD163" s="8">
         <v>19.850684931506848</v>
       </c>
@@ -20987,7 +21978,9 @@
       <c r="AB164" s="8">
         <v>6.8144602941176471</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>12.916103</v>
+      </c>
       <c r="AD164" s="8">
         <v>19.52523857142857</v>
       </c>
@@ -21211,7 +22204,9 @@
       <c r="AB166" s="8">
         <v>6.6079695652173918</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>8.6939709999999994</v>
+      </c>
       <c r="AD166" s="8">
         <v>14.864668</v>
       </c>
@@ -21340,7 +22335,9 @@
       <c r="AB167" s="8">
         <v>8.5686746987951814</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>12.684177</v>
+      </c>
       <c r="AD167" s="8">
         <v>18.655882352941177</v>
       </c>
@@ -21469,7 +22466,9 @@
       <c r="AB168" s="8">
         <v>8.1205357142857135</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>12.454128000000001</v>
+      </c>
       <c r="AD168" s="8">
         <v>18.311749180327869</v>
       </c>
@@ -21598,7 +22597,9 @@
       <c r="AB169" s="8">
         <v>5.2403499999999994</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>13.776403999999999</v>
+      </c>
       <c r="AD169" s="8">
         <v>18.930612244897958</v>
       </c>
@@ -21727,7 +22728,9 @@
       <c r="AB170" s="8">
         <v>4.7942307692307695</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>9.2176860000000005</v>
+      </c>
       <c r="AD170" s="8">
         <v>15.876542592592592</v>
       </c>
@@ -21856,7 +22859,9 @@
       <c r="AB171" s="8">
         <v>2.3263686567164181</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>8.4387480000000004</v>
+      </c>
       <c r="AD171" s="8">
         <v>15.11619</v>
       </c>
@@ -21985,7 +22990,9 @@
       <c r="AB172" s="8">
         <v>7.7625688524590171</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>14.285148</v>
+      </c>
       <c r="AD172" s="8">
         <v>21.090859677419353</v>
       </c>
@@ -22036,7 +23043,7 @@
         <v>19891</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C173" s="4">
         <v>44</v>
@@ -22072,25 +23079,61 @@
       <c t="s" r="N173" s="4">
         <v>52</v>
       </c>
-      <c r="O173" s="5"/>
-      <c r="P173" s="5"/>
-      <c r="Q173" s="6"/>
-      <c r="R173" s="7"/>
-      <c r="S173" s="6"/>
-      <c r="T173" s="6"/>
-      <c r="U173" s="6"/>
-      <c r="V173" s="6"/>
-      <c r="W173" s="6"/>
-      <c r="X173" s="8"/>
-      <c r="Y173" s="6"/>
-      <c r="Z173" s="6"/>
-      <c r="AA173" s="8"/>
-      <c r="AB173" s="8"/>
-      <c r="AC173" s="8"/>
-      <c r="AD173" s="8"/>
-      <c r="AE173" s="6"/>
+      <c r="O173" s="5">
+        <v>8228.5300000000007</v>
+      </c>
+      <c r="P173" s="5">
+        <v>8228.5300000000007</v>
+      </c>
+      <c r="Q173" s="6">
+        <v>0.32460142174601758</v>
+      </c>
+      <c r="R173" s="7">
+        <v>79</v>
+      </c>
+      <c r="S173" s="6">
+        <v>0.21538461538461529</v>
+      </c>
+      <c r="T173" s="6">
+        <v>0.26687514051720052</v>
+      </c>
+      <c r="U173" s="6">
+        <v>-0.021100962140260773</v>
+      </c>
+      <c r="V173" s="6">
+        <v>0.040201712821123572</v>
+      </c>
+      <c r="W173" s="6">
+        <v>0.014544639200440418</v>
+      </c>
+      <c r="X173" s="8">
+        <v>36.024830612244898</v>
+      </c>
+      <c r="Y173" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z173" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA173" s="8">
+        <v>3.6148893333333332</v>
+      </c>
+      <c r="AB173" s="8">
+        <v>22.210714285714285</v>
+      </c>
+      <c r="AC173" s="8">
+        <v>25.756774</v>
+      </c>
+      <c r="AD173" s="8">
+        <v>28.764965306122452</v>
+      </c>
+      <c r="AE173" s="6">
+        <v>0.79591836734693877</v>
+      </c>
       <c r="AF173" s="9"/>
-      <c r="AG173" s="5"/>
+      <c r="AG173" s="5">
+        <v>-17.899999999999999</v>
+      </c>
       <c r="AH173" s="10">
         <v>4</v>
       </c>
@@ -22209,7 +23252,9 @@
       <c r="AB174" s="8">
         <v>4.6581563829787234</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>14.586401</v>
+      </c>
       <c r="AD174" s="8">
         <v>21.164236458333331</v>
       </c>
@@ -22260,7 +23305,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22296,25 +23341,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>4867.3900000000003</v>
+      </c>
+      <c r="P175" s="5">
+        <v>4867.3900000000003</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.21036298033286682</v>
+      </c>
+      <c r="R175" s="7">
+        <v>73</v>
+      </c>
+      <c r="S175" s="6">
+        <v>0.32727272727272738</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.33856888393985274</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.019692936049915868</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.02589919854377808</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.0047845970838580835</v>
+      </c>
+      <c r="X175" s="8">
+        <v>32.851074193548385</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.74193548387096775</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>9.6464651515151516</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>4.8677419354838714</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>14.527418000000001</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>21.486558064516128</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.35483870967741937</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-180.59999999999999</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22431,7 +23512,9 @@
       <c r="AB176" s="8">
         <v>10.347727272727273</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>13.334847999999999</v>
+      </c>
       <c r="AD176" s="8">
         <v>20.291668181818181</v>
       </c>
@@ -22560,7 +23643,9 @@
       <c r="AB177" s="8">
         <v>1.4961538461538462</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>5.7294859999999996</v>
+      </c>
       <c r="AD177" s="8">
         <v>12.683334615384616</v>
       </c>
@@ -22689,7 +23774,9 @@
       <c r="AB178" s="8">
         <v>3.2725</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>8.1675000000000004</v>
+      </c>
       <c r="AD178" s="8">
         <v>15.112500000000001</v>
       </c>
@@ -22943,7 +24030,9 @@
       <c r="AB180" s="8">
         <v>9.8138916666666667</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>17.236964</v>
+      </c>
       <c r="AD180" s="8">
         <v>24.117946153846155</v>
       </c>
@@ -22994,7 +24083,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23030,25 +24119,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>4109.0900000000001</v>
+      </c>
+      <c r="P181" s="5">
+        <v>4109.0900000000001</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.12651880688672001</v>
+      </c>
+      <c r="R181" s="7">
+        <v>45</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.013676994176326146</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.30720913876308376</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.052530608966948888</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.021750071183644068</v>
+      </c>
+      <c r="X181" s="8">
+        <v>13.661538461538461</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.3522222222222222</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>4.7715379999999996</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>9.9160269230769238</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23167,7 +24292,9 @@
       <c r="AB182" s="8">
         <v>3.1425916666666667</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>8.4577150000000003</v>
+      </c>
       <c r="AD182" s="8">
         <v>14.27421320754717</v>
       </c>
@@ -23218,7 +24345,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -23254,25 +24381,61 @@
       <c t="s" r="N183" s="4">
         <v>52</v>
       </c>
-      <c r="O183" s="5"/>
-      <c r="P183" s="5"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="8"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="8"/>
-      <c r="AB183" s="8"/>
-      <c r="AC183" s="8"/>
-      <c r="AD183" s="8"/>
-      <c r="AE183" s="6"/>
+      <c r="O183" s="5">
+        <v>6661.1800000000003</v>
+      </c>
+      <c r="P183" s="5">
+        <v>6661.1800000000003</v>
+      </c>
+      <c r="Q183" s="6">
+        <v>0.34373297937150249</v>
+      </c>
+      <c r="R183" s="7">
+        <v>73</v>
+      </c>
+      <c r="S183" s="6">
+        <v>0.23728813559322037</v>
+      </c>
+      <c r="T183" s="6">
+        <v>-37.08548629522096</v>
+      </c>
+      <c r="U183" s="6">
+        <v>-42.062067021158406</v>
+      </c>
+      <c r="V183" s="6">
+        <v>0.018387282733689825</v>
+      </c>
+      <c r="W183" s="6">
+        <v>-0.0076351337150474844</v>
+      </c>
+      <c r="X183" s="8">
+        <v>23.64673137254902</v>
+      </c>
+      <c r="Y183" s="6">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="Z183" s="6">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AA183" s="8">
+        <v>6.137559154929578</v>
+      </c>
+      <c r="AB183" s="8">
+        <v>2.4696660000000001</v>
+      </c>
+      <c r="AC183" s="8">
+        <v>8.4657440000000008</v>
+      </c>
+      <c r="AD183" s="8">
+        <v>16.349347058823529</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>0.88235294117647056</v>
+      </c>
       <c r="AF183" s="9"/>
-      <c r="AG183" s="5"/>
+      <c r="AG183" s="5">
+        <v>0</v>
+      </c>
       <c r="AH183" s="10">
         <v>4</v>
       </c>
@@ -23391,7 +24554,9 @@
       <c r="AB184" s="8">
         <v>9.1428098039215691</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>14.423463999999999</v>
+      </c>
       <c r="AD184" s="8">
         <v>22.27619107142857</v>
       </c>
@@ -23613,7 +24778,9 @@
       <c r="AB186" s="8">
         <v>8.4679461538461531</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>15.859508</v>
+      </c>
       <c r="AD186" s="8">
         <v>22.096153846153847</v>
       </c>
@@ -23664,7 +24831,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23700,25 +24867,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>2047.3399999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2047.3399999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.19806502154328243</v>
+      </c>
+      <c r="R187" s="7">
+        <v>25</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.21875</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32790352359647157</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.16416520949133998</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.09237938007365655</v>
+      </c>
+      <c r="X187" s="8">
+        <v>29.02745294117647</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>5.9006679999999996</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>10.251043749999999</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>15.464765999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>21.687252941176467</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.76470588235294112</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-194</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23839,7 +25042,9 @@
       <c r="AB188" s="8">
         <v>7.4882722222222222</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>11.885592000000001</v>
+      </c>
       <c r="AD188" s="8">
         <v>18.429762500000002</v>
       </c>
@@ -23890,7 +25095,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23926,25 +25131,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>6725.6999999999998</v>
+      </c>
+      <c r="P189" s="5">
+        <v>6725.6999999999998</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.16977240076666478</v>
+      </c>
+      <c r="R189" s="7">
+        <v>80</v>
+      </c>
+      <c r="S189" s="6">
+        <v>-0.101123595505618</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.33446859062997164</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.031994498713888514</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.05152147731834604</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.026957491413533163</v>
+      </c>
+      <c r="X189" s="8">
+        <v>27.972885074626863</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.044776119402985072</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>6.3039098765432096</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>11.032089552238805</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>17.586317000000001</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>24.503980597014923</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.67164179104477617</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23985,7 +25226,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24021,25 +25262,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>7107.54</v>
+      </c>
+      <c r="P190" s="5">
+        <v>7107.54</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>0.015500675091619565</v>
+      </c>
+      <c r="R190" s="7">
+        <v>75</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.13793103448275867</v>
+      </c>
+      <c r="T190" s="6">
+        <v>-0.20487241717950233</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.66368939182895914</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.045050608227319155</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.024751039037416604</v>
+      </c>
+      <c r="X190" s="8">
+        <v>22.944622580645163</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.74193548387096775</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>4.7846851351351356</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>2.6942517241379313</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>7.3609179999999999</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>14.051612903225807</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.83870967741935487</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-327.58999999999997</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24154,7 +25431,9 @@
       <c r="AB191" s="8">
         <v>10.421794871794871</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>15.716794</v>
+      </c>
       <c r="AD191" s="8">
         <v>22.390832499999998</v>
       </c>
@@ -24281,7 +25560,9 @@
       <c r="AB192" s="8">
         <v>14.922000000000001</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>20.280000000000001</v>
+      </c>
       <c r="AD192" s="8">
         <v>27.226668</v>
       </c>
@@ -24408,7 +25689,9 @@
       <c r="AB193" s="8">
         <v>11.613808571428571</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>16.131495999999999</v>
+      </c>
       <c r="AD193" s="8">
         <v>20.9354175</v>
       </c>
@@ -24539,7 +25822,9 @@
       <c r="AB194" s="8">
         <v>6.3308629629629634</v>
       </c>
-      <c r="AC194" s="8"/>
+      <c r="AC194" s="8">
+        <v>11.299999</v>
+      </c>
       <c r="AD194" s="8">
         <v>18.240122222222222</v>
       </c>
@@ -24685,7 +25970,7 @@
         <v>19945</v>
       </c>
       <c r="B196" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C196" s="4">
         <v>44</v>
@@ -24721,11 +26006,21 @@
       <c t="s" r="N196" s="4">
         <v>52</v>
       </c>
-      <c r="O196" s="5"/>
-      <c r="P196" s="5"/>
-      <c r="Q196" s="6"/>
-      <c r="R196" s="7"/>
-      <c r="S196" s="6"/>
+      <c r="O196" s="5">
+        <v>0</v>
+      </c>
+      <c r="P196" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R196" s="7">
+        <v>0</v>
+      </c>
+      <c r="S196" s="6">
+        <v>-1</v>
+      </c>
       <c r="T196" s="6"/>
       <c r="U196" s="6"/>
       <c r="V196" s="6"/>
@@ -24733,13 +26028,17 @@
       <c r="X196" s="8"/>
       <c r="Y196" s="6"/>
       <c r="Z196" s="6"/>
-      <c r="AA196" s="8"/>
+      <c r="AA196" s="8">
+        <v>8.7583500000000001</v>
+      </c>
       <c r="AB196" s="8"/>
       <c r="AC196" s="8"/>
       <c r="AD196" s="8"/>
       <c r="AE196" s="6"/>
       <c r="AF196" s="9"/>
-      <c r="AG196" s="5"/>
+      <c r="AG196" s="5">
+        <v>0</v>
+      </c>
       <c r="AH196" s="10">
         <v>1</v>
       </c>
@@ -24858,7 +26157,9 @@
       <c r="AB197" s="8">
         <v>5.4773333333333332</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>7.7838260000000004</v>
+      </c>
       <c r="AD197" s="8">
         <v>14.212393589743591</v>
       </c>
@@ -24987,7 +26288,9 @@
       <c r="AB198" s="8">
         <v>1.1566700000000001</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>9.1989730000000005</v>
+      </c>
       <c r="AD198" s="8">
         <v>15.766666666666666</v>
       </c>
@@ -25116,7 +26419,9 @@
       <c r="AB199" s="8">
         <v>10.442459523809523</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>15.315474999999999</v>
+      </c>
       <c r="AD199" s="8">
         <v>22.246826190476192</v>
       </c>
@@ -25167,7 +26472,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25203,25 +26508,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>1536.1800000000001</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1536.1800000000001</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.4124810206946139</v>
+      </c>
+      <c r="R200" s="7">
+        <v>23</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.34285714285714286</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0.46692841984663258</v>
+      </c>
+      <c r="U200" s="6">
+        <v>0.063505643869859005</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.14214740460102332</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.063100678305927693</v>
+      </c>
+      <c r="X200" s="8">
+        <v>24.635412500000001</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>4.6652173913043473</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>2.7541625000000001</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>7.3124989999999999</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>14.275</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-66.900000000000006</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25433,7 +26774,9 @@
       <c r="AB202" s="8">
         <v>8.817817241379311</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>15.063927</v>
+      </c>
       <c r="AD202" s="8">
         <v>21.548889999999997</v>
       </c>
@@ -25655,7 +26998,9 @@
       <c r="AB204" s="8">
         <v>5.1301571428571426</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>17.894551</v>
+      </c>
       <c r="AD204" s="8">
         <v>24.546213636363635</v>
       </c>
@@ -25780,7 +27125,9 @@
       <c r="AB205" s="8">
         <v>1.9012846153846152</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>6.6489010000000004</v>
+      </c>
       <c r="AD205" s="8">
         <v>13.355950000000002</v>
       </c>
@@ -25831,7 +27178,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25867,25 +27214,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>3248.2800000000002</v>
+      </c>
+      <c r="P206" s="5">
+        <v>3248.2800000000002</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>38</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.34399546837095324</v>
+      </c>
+      <c r="U206" s="6">
+        <v>-0.0087019591907101599</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.03159379733274225</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.01548989003411036</v>
+      </c>
+      <c r="X206" s="8">
+        <v>47.438886666666669</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>12.864913157894737</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>14.014446666666666</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>25.828887999999999</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>32.767780000000002</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.20000000000000001</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-141.69999999999999</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -26000,7 +27379,9 @@
       <c r="AB207" s="8">
         <v>7.3156249999999998</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>15.984252</v>
+      </c>
       <c r="AD207" s="8">
         <v>22.309805882352943</v>
       </c>
@@ -26125,7 +27506,9 @@
       <c r="AB208" s="8">
         <v>2.5655804347826088</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>6.504912</v>
+      </c>
       <c r="AD208" s="8">
         <v>13.41558043478261</v>
       </c>
@@ -26434,7 +27817,9 @@
       <c r="AB211" s="8">
         <v>3.2309514285714283</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>11.247617999999999</v>
+      </c>
       <c r="AD211" s="8">
         <v>18.190951428571431</v>
       </c>
@@ -26909,22 +28294,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26934,10 +28321,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-169</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.575.495,35</t>
-  </si>
-  <si>
-    <t>R$ 8.752,75
-R$ 8.991,71</t>
+171</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 1.595.023,95</t>
+  </si>
+  <si>
+    <t>R$ 8.763,87
+R$ 9.000,75</t>
   </si>
   <si>
     <t>2.1%
-4.5%</t>
-  </si>
-  <si>
-    <t>93.3</t>
+4.4%</t>
+  </si>
+  <si>
+    <t>93.4</t>
   </si>
   <si>
     <t>(2.3%)</t>
   </si>
   <si>
-    <t>14.5%</t>
-  </si>
-  <si>
-    <t>(25.1%)</t>
-  </si>
-  <si>
-    <t>2.7%</t>
+    <t>14.7%</t>
+  </si>
+  <si>
+    <t>(24.8%)</t>
+  </si>
+  <si>
+    <t>2.8%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>15.0%</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>20.8</t>
-  </si>
-  <si>
-    <t>64.5%</t>
-  </si>
-  <si>
-    <t>-R$ 45.977,61</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>60.3%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>20.9</t>
+  </si>
+  <si>
+    <t>64.1%</t>
+  </si>
+  <si>
+    <t>-R$ 46.054,31</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2999,10 +2999,10 @@
         <v>0.068181818181818121</v>
       </c>
       <c r="T13" s="6">
-        <v>0.35266000427091371</v>
+        <v>0.36734083957897057</v>
       </c>
       <c r="U13" s="6">
-        <v>0.0038167674694147471</v>
+        <v>0.018497602777471617</v>
       </c>
       <c r="V13" s="6">
         <v>0.029496109679819246</v>
@@ -6672,7 +6672,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6708,25 +6708,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>11495.01</v>
+      </c>
+      <c r="P42" s="5">
+        <v>11495.01</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.18082958984826436</v>
+      </c>
+      <c r="R42" s="7">
+        <v>114</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.23913043478260865</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.40553731575701107</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.04318965359751753</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.028141167341307227</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0039358817434695581</v>
+      </c>
+      <c r="X42" s="8">
+        <v>42.169963736263739</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.40659340659340659</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.45054945054945056</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>10.918233333333333</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>15.1837</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>27.028020999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>33.957875824175829</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.36263736263736263</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -14154,7 +14190,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14190,25 +14226,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>8033.5900000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>8033.5900000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.1226956480906134</v>
+      </c>
+      <c r="R102" s="7">
+        <v>79</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.15957446808510634</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.23318655793985005</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.077774046223419421</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.049633787634171027</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.034621819136898942</v>
+      </c>
+      <c r="X102" s="8">
+        <v>42.317707812499997</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.09375</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.53125</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>13.792073170731708</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>13.857778333333332</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>27.657520000000002</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>32.858332812500002</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-76.700000000000003</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -15295,7 +15367,9 @@
       <c r="AB111" s="8">
         <v>0.99310344827586206</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.2999989999999997</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.258620689655173</v>
       </c>
@@ -17190,7 +17264,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18367,7 +18441,7 @@
         <v>-168.09999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -21861,7 +21935,7 @@
         <v>-654.33000000000004</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -27926,7 +28000,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 1.595.023,95</t>
-  </si>
-  <si>
-    <t>R$ 8.763,87
-R$ 9.000,75</t>
-  </si>
-  <si>
-    <t>2.1%
-4.4%</t>
-  </si>
-  <si>
-    <t>93.4</t>
-  </si>
-  <si>
-    <t>(2.3%)</t>
-  </si>
-  <si>
-    <t>14.7%</t>
-  </si>
-  <si>
-    <t>(24.8%)</t>
-  </si>
-  <si>
-    <t>2.8%</t>
+173</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.616.487,81</t>
+  </si>
+  <si>
+    <t>R$ 8.785,26
+R$ 9.020,76</t>
+  </si>
+  <si>
+    <t>2.4%
+4.7%</t>
+  </si>
+  <si>
+    <t>93.6</t>
+  </si>
+  <si>
+    <t>(2.0%)</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>(24.6%)</t>
+  </si>
+  <si>
+    <t>2.7%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -950,10 +950,10 @@
     <t>29.5</t>
   </si>
   <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>15.5%</t>
+    <t>59.9%</t>
+  </si>
+  <si>
+    <t>15.4%</t>
   </si>
   <si>
     <t>6.2</t>
@@ -962,19 +962,19 @@
     <t>7.8</t>
   </si>
   <si>
-    <t>14.4</t>
+    <t>14.3</t>
   </si>
   <si>
     <t>20.9</t>
   </si>
   <si>
-    <t>64.1%</t>
-  </si>
-  <si>
-    <t>-R$ 46.054,31</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>-R$ 46.750,91</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>0.073394495412844041</v>
       </c>
       <c r="T7" s="6">
-        <v>0.3381100470738771</v>
+        <v>0.33991881394878648</v>
       </c>
       <c r="U7" s="6">
-        <v>0.0080251405338486008</v>
+        <v>0.0098339074087580112</v>
       </c>
       <c r="V7" s="6">
         <v>0.041526286684435157</v>
@@ -8720,7 +8720,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8756,25 +8756,59 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>11248.040000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>11248.040000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.19434979416439901</v>
+      </c>
+      <c r="R58" s="7">
+        <v>129</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.10256410256410264</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.27312558454628538</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.078976648376072628</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011054459265792084</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.00041687262847571661</v>
+      </c>
+      <c r="X58" s="8">
+        <v>28.762138043478263</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.11956521739130435</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.765079365079365</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.1548913043478262</v>
+      </c>
       <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>19.319203260869564</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.55434782608695654</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-275.39999999999998</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -16871,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -21096,9 +21130,7 @@
       <c r="AB156" s="8">
         <v>4.6961982456140348</v>
       </c>
-      <c r="AC156" s="8">
-        <v>18.980875000000001</v>
-      </c>
+      <c r="AC156" s="8"/>
       <c r="AD156" s="8">
         <v>25.264246774193548</v>
       </c>
@@ -25949,7 +25981,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25985,25 +26017,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>10215.82</v>
+      </c>
+      <c r="P195" s="5">
+        <v>10215.82</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.50156464734803663</v>
+      </c>
+      <c r="R195" s="7">
+        <v>107</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.25882352941176467</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.33414191910194191</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0084473199410326338</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.017905904763396378</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0023378935807404598</v>
+      </c>
+      <c r="X195" s="8">
+        <v>27.54189189189189</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.32432432432432434</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>5.7626168224299068</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>6.5700445945945942</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>19.646171621621622</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.66216216216216217</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-421.19999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.616.487,81</t>
-  </si>
-  <si>
-    <t>R$ 8.785,26
-R$ 9.020,76</t>
-  </si>
-  <si>
-    <t>2.4%
-4.7%</t>
-  </si>
-  <si>
-    <t>93.6</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.628.688,87</t>
+  </si>
+  <si>
+    <t>R$ 8.803,72
+R$ 9.039,04</t>
+  </si>
+  <si>
+    <t>2.5%
+4.9%</t>
+  </si>
+  <si>
+    <t>93.8</t>
   </si>
   <si>
     <t>(2.0%)</t>
   </si>
   <si>
-    <t>15.0%</t>
-  </si>
-  <si>
-    <t>(24.6%)</t>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>(24.4%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,7 +950,7 @@
     <t>29.5</t>
   </si>
   <si>
-    <t>59.9%</t>
+    <t>59.7%</t>
   </si>
   <si>
     <t>15.4%</t>
@@ -971,7 +971,7 @@
     <t>64.0%</t>
   </si>
   <si>
-    <t>-R$ 46.750,91</t>
+    <t>-R$ 46.847,61</t>
   </si>
   <si>
     <t>2.95</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>9.7954025862068956</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>17.604310000000002</v>
+      </c>
       <c r="AD13" s="8">
         <v>24.529454310344828</v>
       </c>
@@ -8798,7 +8800,9 @@
       <c r="AB58" s="8">
         <v>7.1548913043478262</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.384238</v>
+      </c>
       <c r="AD58" s="8">
         <v>19.319203260869564</v>
       </c>
@@ -10982,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -11016,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>12201.059999999999</v>
+      </c>
+      <c r="P76" s="5">
+        <v>12201.059999999999</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.25077372086181082</v>
+      </c>
+      <c r="R76" s="7">
+        <v>134</v>
+      </c>
+      <c r="S76" s="6">
+        <v>0.055118110236220375</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.33243519005725736</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.050615954679347534</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.014253679598329981</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.0054069072687127186</v>
+      </c>
+      <c r="X76" s="8">
+        <v>27.908453623188404</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.20289855072463769</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.15942028985507245</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>5.3202205882352942</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>8.0582046153846161</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>13.6852</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>21.70193188405797</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.60869565217391308</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-96.700000000000003</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -21130,7 +21170,9 @@
       <c r="AB156" s="8">
         <v>4.6961982456140348</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>18.980875000000001</v>
+      </c>
       <c r="AD156" s="8">
         <v>25.264246774193548</v>
       </c>
@@ -24009,7 +24051,9 @@
       <c r="AB179" s="8">
         <v>1.2321977272727274</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.4166650000000001</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.367424999999999</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.628.688,87</t>
-  </si>
-  <si>
-    <t>R$ 8.803,72
-R$ 9.039,04</t>
-  </si>
-  <si>
-    <t>2.5%
-4.9%</t>
+176</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 1.646.959,68</t>
+  </si>
+  <si>
+    <t>R$ 8.807,27
+R$ 9.040,13</t>
+  </si>
+  <si>
+    <t>2.1%
+4.4%</t>
   </si>
   <si>
     <t>93.8</t>
   </si>
   <si>
-    <t>(2.0%)</t>
-  </si>
-  <si>
-    <t>15.1%</t>
-  </si>
-  <si>
-    <t>(24.4%)</t>
+    <t>(2.4%)</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>(18.5%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>29.5</t>
   </si>
   <si>
-    <t>59.7%</t>
-  </si>
-  <si>
-    <t>15.4%</t>
+    <t>59.9%</t>
+  </si>
+  <si>
+    <t>15.3%</t>
   </si>
   <si>
     <t>6.2</t>
@@ -971,10 +971,10 @@
     <t>64.0%</t>
   </si>
   <si>
-    <t>-R$ 46.847,61</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>-R$ 47.223,91</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2999,10 +2999,10 @@
         <v>0.068181818181818121</v>
       </c>
       <c r="T13" s="6">
-        <v>0.36734083957897057</v>
+        <v>0.35266000427091371</v>
       </c>
       <c r="U13" s="6">
-        <v>0.018497602777471617</v>
+        <v>0.0038167674694147471</v>
       </c>
       <c r="V13" s="6">
         <v>0.029496109679819246</v>
@@ -4388,7 +4388,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4424,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>9005.9300000000003</v>
+      </c>
+      <c r="P24" s="5">
+        <v>9005.9300000000003</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.16342428354991012</v>
+      </c>
+      <c r="R24" s="7">
+        <v>100</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.15254237288135597</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0.0055900945266063578</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.33696531063421548</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.024380880153410028</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0053922804196790339</v>
+      </c>
+      <c r="X24" s="8">
+        <v>30.993426760563381</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.85915492957746475</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.14084507042253522</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>5.7928571428571436</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>9.4881637681159425</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>22.329577464788734</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.60563380281690138</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-166.5</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5710,10 +5744,10 @@
         <v>0.38607594936708867</v>
       </c>
       <c r="T34" s="6">
-        <v>0.32885206918791543</v>
+        <v>-1.2907588249633086</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.016284488581251616</v>
+        <v>-1.6358953827324758</v>
       </c>
       <c r="V34" s="6">
         <v>0.057699434521844672</v>
@@ -12604,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12677,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12711,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>9264.8799999999992</v>
+      </c>
+      <c r="P89" s="5">
+        <v>9264.8799999999992</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.32878655498225784</v>
+      </c>
+      <c r="R89" s="7">
+        <v>81</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.42142857142857137</v>
+      </c>
+      <c r="T89" s="6">
+        <v>13.385636370897412</v>
+      </c>
+      <c r="U89" s="6">
+        <v>13.059659132120439</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.022770991097564135</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0093245136472355824</v>
+      </c>
+      <c r="X89" s="8">
+        <v>28.715590322580645</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.5650402439024393</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>4.5016129032258068</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>18.689248387096775</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.58064516129032262</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-209.80000000000001</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16683,7 +16751,7 @@
         <v>-69.799999999999997</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18646,7 +18714,7 @@
         <v>-73.799999999999997</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20924,7 +20992,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-18).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 1.646.959,68</t>
-  </si>
-  <si>
-    <t>R$ 8.807,27
-R$ 9.040,13</t>
-  </si>
-  <si>
-    <t>2.1%
-4.4%</t>
-  </si>
-  <si>
-    <t>93.8</t>
-  </si>
-  <si>
-    <t>(2.4%)</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>(18.5%)</t>
+180</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.682.755,03</t>
+  </si>
+  <si>
+    <t>R$ 8.810,24
+R$ 9.038,10</t>
+  </si>
+  <si>
+    <t>2.3%
+4.5%</t>
+  </si>
+  <si>
+    <t>93.9</t>
+  </si>
+  <si>
+    <t>(1.9%)</t>
+  </si>
+  <si>
+    <t>21.1%</t>
+  </si>
+  <si>
+    <t>(18.2%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,19 +947,19 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>59.9%</t>
-  </si>
-  <si>
-    <t>15.3%</t>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>60.6%</t>
+  </si>
+  <si>
+    <t>15.2%</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>7.8</t>
+    <t>7.7</t>
   </si>
   <si>
     <t>14.3</t>
@@ -971,7 +971,7 @@
     <t>64.0%</t>
   </si>
   <si>
-    <t>-R$ 47.223,91</t>
+    <t>-R$ 47.277,64</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>17368.380000000001</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17368.380000000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.24269962143137724</v>
+      </c>
+      <c r="R6" s="7">
+        <v>186</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.35766423357664223</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.32738349805796507</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.0079052277759929235</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.024844441450497974</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0028389348920279263</v>
+      </c>
+      <c r="X6" s="8">
+        <v>23.449885616438358</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.95890410958904104</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.0068493150684931503</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>7.7680107526881716</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.4987358620689655</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>10.399533999999999</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>17.316666438356165</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.84931506849315064</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -5958,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5994,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>9232.7299999999996</v>
+      </c>
+      <c r="P36" s="5">
+        <v>9232.7299999999996</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.47595449073844631</v>
+      </c>
+      <c r="R36" s="7">
+        <v>124</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.9076923076923078</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.31437383092541427</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.0057727995944861377</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.057094922086966704</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.02780131120481158</v>
+      </c>
+      <c r="X36" s="8">
+        <v>31.685274757281551</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.88349514563106801</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.22330097087378642</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>7.8822664000000007</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>9.5642398058252436</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>17.701778999999998</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>24.658575728155338</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.5436893203883495</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-11.83</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7879,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7915,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>872.77999999999997</v>
+      </c>
+      <c r="P51" s="5">
+        <v>872.77999999999997</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.061763238890037764</v>
+      </c>
+      <c r="R51" s="7">
+        <v>8</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.3493549348060222</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.035163500538509133</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.12657256124109167</v>
+      </c>
+      <c r="X51" s="8">
+        <v>30.183350000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.1979125000000002</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>9.5416500000000006</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>15.299999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>22.24165</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -21386,7 +21494,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21422,25 +21530,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>8321.4599999999991</v>
+      </c>
+      <c r="P158" s="5">
+        <v>8321.4599999999991</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.22918540488918249</v>
+      </c>
+      <c r="R158" s="7">
+        <v>81</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.21359223300970875</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.29846873024685577</v>
+      </c>
+      <c r="U158" s="6">
+        <v>1.8698641824872078E-05</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.027260660989778238</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0075225381123024092</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.770454545454545</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.9812753086419752</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.5931818181818183</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>10.600756000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>17.547727272727276</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.45454545454545453</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26171,7 +26315,9 @@
       <c r="AB195" s="8">
         <v>6.5700445945945942</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>12.669824999999999</v>
+      </c>
       <c r="AD195" s="8">
         <v>19.646171621621622</v>
       </c>
